--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -197,21 +197,21 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,256 +227,256 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>LUIS HUGO</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>DEL CARMEN</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SUSUNAGA</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CID</t>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
   </si>
   <si>
     <t>NAOMI</t>
   </si>
   <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>ARELY</t>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>OFELIA</t>
+  </si>
+  <si>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
   </si>
   <si>
     <t>MARIA GUADALUPE</t>
   </si>
   <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
     <t>PERLA</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>LUIS HUGO</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>NOE</t>
+  </si>
+  <si>
+    <t>MERIELING YAMILETH</t>
+  </si>
+  <si>
+    <t>SAIRA YAMILET</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
   </si>
   <si>
     <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>NOE</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
-  </si>
-  <si>
-    <t>SAIRA YAMILET</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
   </si>
   <si>
     <t>BRENDA ELENA</t>
@@ -986,10 +986,10 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1001,7 +1001,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1025,7 +1025,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -1063,10 +1063,10 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1078,7 +1078,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1099,7 +1099,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1125,7 +1125,7 @@
         <v>-1</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -1143,7 +1143,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1155,7 +1155,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1179,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1217,10 +1217,10 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1232,7 +1232,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1253,10 +1253,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1268,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1294,10 +1294,10 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1309,7 +1309,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1386,7 +1386,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1448,10 +1448,10 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1525,10 +1525,10 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1564,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1576,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1602,10 +1602,10 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1617,7 +1617,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1641,7 +1641,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1653,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1679,10 +1679,10 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1741,7 +1741,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1756,10 +1756,10 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1795,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1818,7 +1818,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -1833,10 +1833,10 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1848,7 +1848,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1872,7 +1872,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1884,7 +1884,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1910,10 +1910,10 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1987,10 +1987,10 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2023,10 +2023,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2064,10 +2064,10 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2103,7 +2103,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2141,10 +2141,10 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2218,10 +2218,10 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2233,7 +2233,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2257,7 +2257,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2295,10 +2295,10 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2310,7 +2310,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2334,7 +2334,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2372,10 +2372,10 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2387,7 +2387,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2408,10 +2408,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2434,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -2449,10 +2449,10 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2464,7 +2464,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2488,7 +2488,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2526,10 +2526,10 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2541,7 +2541,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2603,10 +2603,10 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2618,7 +2618,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2680,10 +2680,10 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2760,7 +2760,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2772,7 +2772,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2926,7 +2926,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2988,10 +2988,10 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3003,7 +3003,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3024,7 +3024,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3056,13 +3056,13 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3074,13 +3074,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3106,10 +3106,10 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3121,7 +3121,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3145,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3157,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3183,10 +3183,10 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3198,7 +3198,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3242,10 +3242,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -3260,7 +3260,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3275,7 +3275,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3296,10 +3296,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3337,10 +3337,10 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3352,7 +3352,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3376,7 +3376,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3388,7 +3388,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3414,10 +3414,10 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3429,7 +3429,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3453,7 +3453,7 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3491,10 +3491,10 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3506,7 +3506,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3565,7 +3565,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3583,7 +3583,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3609,10 +3609,10 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3624,7 +3624,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3645,10 +3645,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3660,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3701,7 +3701,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3825,34 +3825,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>67.56999999999999</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>32.43</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3866,25 +3866,25 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>68.56999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="G4">
-        <v>2.86</v>
+        <v>14.29</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>28.57</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3898,89 +3898,89 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="G5">
-        <v>11.11</v>
+        <v>8.33</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>16.67</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>8.33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>81.08</v>
+      </c>
+      <c r="G7">
+        <v>18.92</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>80</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.6</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,10 +4025,10 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4045,150 +4045,150 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920360</v>
+        <v>19330051920367</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920426</v>
+        <v>19330051920435</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920367</v>
+        <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920367</v>
+        <v>19330051920383</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920435</v>
+        <v>19330051920386</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920375</v>
+        <v>19330051920386</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920377</v>
+        <v>19330051920386</v>
       </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4199,76 +4199,76 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920383</v>
+        <v>19330051920386</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920383</v>
+        <v>19330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -4279,16 +4279,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -4299,321 +4299,161 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920386</v>
+        <v>19330051920436</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920419</v>
+        <v>19330051920393</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920419</v>
+        <v>19330051920399</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920419</v>
+        <v>19330051920399</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920419</v>
+        <v>19330051920399</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920436</v>
+        <v>19330051920399</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920393</v>
+        <v>19330051920399</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920393</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920393</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920369</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920399</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920399</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920399</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920399</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920399</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4653,13 +4493,13 @@
         <v>19330051920386</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -4670,13 +4510,13 @@
         <v>19330051920399</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -4687,13 +4527,13 @@
         <v>19330051920419</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -4707,30 +4547,30 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920393</v>
+        <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4738,47 +4578,47 @@
         <v>19330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920383</v>
+        <v>19330051920435</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920426</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4786,16 +4626,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920435</v>
+        <v>19330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4803,81 +4643,81 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920375</v>
+        <v>19330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920377</v>
+        <v>19330051920358</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920436</v>
+        <v>19330051920456</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920369</v>
+        <v>19330051920362</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920359</v>
+        <v>19330051920426</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -4888,13 +4728,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
         <v>134</v>
@@ -4905,16 +4745,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920456</v>
+        <v>19330051920365</v>
       </c>
       <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
         <v>106</v>
       </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4922,16 +4762,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920362</v>
+        <v>19330051920368</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4939,16 +4779,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920366</v>
+        <v>19330051920371</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4956,13 +4796,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920365</v>
+        <v>18330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4973,16 +4813,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920368</v>
+        <v>19330051920372</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4990,16 +4830,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920371</v>
+        <v>19330051920373</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5007,16 +4847,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>18330051920097</v>
+        <v>19330051920375</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5024,16 +4864,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920372</v>
+        <v>19330051920374</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5041,13 +4881,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920373</v>
+        <v>19330051920376</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
         <v>141</v>
@@ -5058,13 +4898,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920374</v>
+        <v>19330051920377</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
         <v>142</v>
@@ -5075,13 +4915,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920376</v>
+        <v>19330051920378</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -5092,13 +4932,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920378</v>
+        <v>19330051920381</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -5109,13 +4949,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920381</v>
+        <v>19330051920382</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -5126,13 +4966,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920382</v>
+        <v>19330051920389</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -5143,13 +4983,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920389</v>
+        <v>18330051920108</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -5160,13 +5000,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>18330051920108</v>
+        <v>19330051920391</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -5177,13 +5017,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920391</v>
+        <v>19330051920394</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -5194,13 +5034,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920394</v>
+        <v>19330051920434</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>150</v>
@@ -5211,13 +5051,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920434</v>
+        <v>19330051920396</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>151</v>
@@ -5228,13 +5068,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920396</v>
+        <v>19330051920369</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
         <v>152</v>
@@ -5248,10 +5088,10 @@
         <v>18330051920188</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>153</v>
@@ -5265,10 +5105,10 @@
         <v>19330051920398</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>154</v>
@@ -5284,7 +5124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5316,22 +5156,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
         <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5339,22 +5179,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5362,22 +5202,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920377</v>
+        <v>19330051920436</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5385,16 +5225,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920377</v>
+        <v>19330051920436</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5408,39 +5248,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920426</v>
+        <v>18330051920188</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920097</v>
+        <v>18330051920188</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5454,39 +5294,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920375</v>
+        <v>18330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920108</v>
+        <v>19330051920377</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5500,47 +5340,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920369</v>
+        <v>18330051920108</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920398</v>
-      </c>
-      <c r="B11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -998,7 +998,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1188,7 +1188,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1460,7 +1460,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1537,7 +1537,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1614,7 +1614,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1691,7 +1691,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1804,7 +1804,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1922,7 +1922,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1999,7 +1999,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2076,7 +2076,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2112,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2307,7 +2307,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2384,7 +2384,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2538,7 +2538,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2574,7 +2574,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2615,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2769,7 +2769,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2828,7 +2828,7 @@
         <v>-1</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -2846,7 +2846,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -2882,7 +2882,7 @@
         <v>-1</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2905,7 +2905,7 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -2923,7 +2923,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2959,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3000,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3059,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -3118,7 +3118,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3195,7 +3195,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3272,7 +3272,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3349,7 +3349,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>8</v>
@@ -3426,7 +3426,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3562,7 +3562,7 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>7</v>
@@ -3621,7 +3621,7 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -3680,7 +3680,7 @@
         <v>-1</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3698,7 +3698,7 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3734,7 +3734,7 @@
         <v>-1</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3802,25 +3802,25 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>62.16</v>
+        <v>56.76</v>
       </c>
       <c r="G2">
-        <v>27.03</v>
+        <v>43.24</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4039,36 +4039,36 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920360</v>
+        <v>19330051920367</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920367</v>
+        <v>19330051920435</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4079,16 +4079,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920435</v>
+        <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4111,30 +4111,30 @@
         <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920383</v>
+        <v>19330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4151,10 +4151,10 @@
         <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4171,10 +4171,10 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4191,50 +4191,50 @@
         <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4251,110 +4251,110 @@
         <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920419</v>
+        <v>19330051920436</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920419</v>
+        <v>19330051920393</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920419</v>
+        <v>19330051920399</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920436</v>
+        <v>19330051920399</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920393</v>
+        <v>19330051920399</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4371,90 +4371,10 @@
         <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920399</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920399</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920399</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920399</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4502,7 +4422,7 @@
         <v>89</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4519,7 +4439,7 @@
         <v>93</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4536,21 +4456,21 @@
         <v>90</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920360</v>
+        <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4558,19 +4478,19 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920383</v>
+        <v>19330051920360</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5124,7 +5044,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5340,16 +5260,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920108</v>
+        <v>19330051920378</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5358,6 +5278,52 @@
         <v>58</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>18330051920108</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920369</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -206,12 +206,12 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,55 +227,193 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>LUIS HUGO</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SUSUNAGA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
   </si>
   <si>
     <t>CID</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>MELCHOR</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>OFELIA</t>
   </si>
   <si>
     <t>ZURI SADAY</t>
@@ -284,187 +422,49 @@
     <t>ARELY</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>LUIS HUGO</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
   </si>
   <si>
     <t>ASTRID</t>
   </si>
   <si>
+    <t>NOE</t>
+  </si>
+  <si>
     <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>NOE</t>
   </si>
   <si>
     <t>MERIELING YAMILETH</t>
@@ -995,7 +995,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -1069,10 +1069,10 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1108,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1223,10 +1223,10 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1300,10 +1300,10 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1454,10 +1454,10 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1490,10 +1490,10 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1531,10 +1531,10 @@
         <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1567,10 +1567,10 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1593,7 +1593,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1685,10 +1685,10 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -1724,7 +1724,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1762,10 +1762,10 @@
         <v>4</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -1878,7 +1878,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1916,10 +1916,10 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1952,10 +1952,10 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1993,10 +1993,10 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2032,7 +2032,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2070,10 +2070,10 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2109,7 +2109,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2147,10 +2147,10 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2183,10 +2183,10 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2224,10 +2224,10 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2260,10 +2260,10 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2301,10 +2301,10 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2340,7 +2340,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2378,10 +2378,10 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2417,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2455,10 +2455,10 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2491,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2532,10 +2532,10 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2609,10 +2609,10 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2648,7 +2648,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2686,10 +2686,10 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2725,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2748,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -2802,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2822,10 +2822,10 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -2876,10 +2876,10 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2994,10 +2994,10 @@
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3033,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3094,7 +3094,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3115,7 +3115,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -3148,10 +3148,10 @@
         <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3189,10 +3189,10 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -3225,10 +3225,10 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3251,7 +3251,7 @@
         <v>5</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -3269,7 +3269,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -3305,7 +3305,7 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3343,10 +3343,10 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -3420,10 +3420,10 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -3456,10 +3456,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3497,10 +3497,10 @@
         <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>7</v>
@@ -3615,10 +3615,10 @@
         <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -3651,10 +3651,10 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3674,10 +3674,10 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>5</v>
@@ -3728,10 +3728,10 @@
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>5</v>
@@ -3834,25 +3834,25 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>30.56</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3921,66 +3921,66 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>81.08</v>
+      </c>
+      <c r="G6">
+        <v>18.92</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.6</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>81.08</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G7">
-        <v>18.92</v>
+        <v>11.43</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,10 +4025,10 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4039,342 +4039,162 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920367</v>
+        <v>19330051920383</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920435</v>
+        <v>19330051920386</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920383</v>
+        <v>19330051920386</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
         <v>79</v>
       </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920383</v>
+        <v>19330051920419</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
         <v>80</v>
       </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920386</v>
+        <v>19330051920399</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920386</v>
+        <v>19330051920399</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920419</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920419</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920419</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920436</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920393</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920399</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920399</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920399</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920399</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4410,84 +4230,84 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920386</v>
+        <v>19330051920419</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920399</v>
+        <v>19330051920386</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920419</v>
+        <v>19330051920399</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>81</v>
       </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920383</v>
+        <v>19330051920360</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920360</v>
+        <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4495,81 +4315,81 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920367</v>
+        <v>19330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920435</v>
+        <v>19330051920358</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920436</v>
+        <v>19330051920456</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920393</v>
+        <v>19330051920362</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920359</v>
+        <v>19330051920426</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>129</v>
@@ -4580,13 +4400,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>130</v>
@@ -4597,16 +4417,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920456</v>
+        <v>19330051920365</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4614,16 +4434,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920362</v>
+        <v>19330051920368</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4631,16 +4451,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920426</v>
+        <v>19330051920367</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4648,16 +4468,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920366</v>
+        <v>19330051920435</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4665,13 +4485,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920365</v>
+        <v>19330051920371</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4682,13 +4502,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920368</v>
+        <v>18330051920097</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -4699,16 +4519,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920371</v>
+        <v>19330051920372</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4716,16 +4536,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>18330051920097</v>
+        <v>19330051920373</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4733,16 +4553,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920372</v>
+        <v>19330051920375</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4750,13 +4570,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920373</v>
+        <v>19330051920374</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>138</v>
@@ -4767,13 +4587,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920375</v>
+        <v>19330051920376</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>139</v>
@@ -4784,13 +4604,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920374</v>
+        <v>19330051920377</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>140</v>
@@ -4801,13 +4621,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920376</v>
+        <v>19330051920378</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>141</v>
@@ -4818,13 +4638,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920377</v>
+        <v>19330051920381</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>142</v>
@@ -4835,13 +4655,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920378</v>
+        <v>19330051920382</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -4852,13 +4672,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920381</v>
+        <v>19330051920389</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -4869,13 +4689,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920382</v>
+        <v>18330051920108</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4886,13 +4706,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920389</v>
+        <v>19330051920436</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -4903,13 +4723,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>18330051920108</v>
+        <v>19330051920391</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4920,13 +4740,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920391</v>
+        <v>19330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4940,10 +4760,10 @@
         <v>19330051920394</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -4957,10 +4777,10 @@
         <v>19330051920434</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>150</v>
@@ -4974,10 +4794,10 @@
         <v>19330051920396</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>151</v>
@@ -4991,10 +4811,10 @@
         <v>19330051920369</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>152</v>
@@ -5008,10 +4828,10 @@
         <v>18330051920188</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
         <v>153</v>
@@ -5025,10 +4845,10 @@
         <v>19330051920398</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
         <v>154</v>
@@ -5044,7 +4864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5076,22 +4896,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5099,16 +4919,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5122,16 +4942,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920436</v>
+        <v>19330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5140,21 +4960,21 @@
         <v>59</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920436</v>
+        <v>19330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5168,16 +4988,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920188</v>
+        <v>19330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5191,16 +5011,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920188</v>
+        <v>19330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5214,22 +5034,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920097</v>
+        <v>18330051920188</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5237,16 +5057,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920377</v>
+        <v>18330051920188</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5260,16 +5080,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920378</v>
+        <v>18330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5283,16 +5103,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920108</v>
+        <v>19330051920377</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5306,16 +5126,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920369</v>
+        <v>19330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -5324,6 +5144,29 @@
         <v>58</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>18330051920108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -3668,7 +3668,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>-1</v>
@@ -3722,7 +3722,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -3901,22 +3901,22 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>77.78</v>
       </c>
       <c r="G5">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4171,29 +4171,9 @@
         <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920399</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4264,33 +4244,33 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920399</v>
+        <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920360</v>
+        <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4298,16 +4278,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920383</v>
+        <v>19330051920399</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -224,21 +224,129 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>VICENTE</t>
   </si>
   <si>
+    <t>SUSUNAGA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
@@ -248,12 +356,90 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>VERGEL</t>
   </si>
   <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>OFELIA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -263,226 +449,40 @@
     <t>DIANA LAURA</t>
   </si>
   <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>NOE</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>MERIELING YAMILETH</t>
+  </si>
+  <si>
+    <t>SAIRA YAMILET</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
     <t>PAULINA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>NOE</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
-  </si>
-  <si>
-    <t>SAIRA YAMILET</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>BRENDA ELENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -1004,25 +1004,25 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -1034,10 +1034,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1081,22 +1081,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1140,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -1158,28 +1158,28 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1191,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1235,25 +1235,25 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1268,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1312,28 +1312,28 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1380,7 +1380,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1389,22 +1389,22 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1466,22 +1466,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1543,22 +1543,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1573,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1620,28 +1620,28 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1650,10 +1650,10 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1697,28 +1697,28 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1727,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1774,25 +1774,25 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1804,7 +1804,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1851,25 +1851,25 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1928,28 +1928,28 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1958,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2005,25 +2005,25 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -2035,10 +2035,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2082,22 +2082,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2159,22 +2159,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2236,25 +2236,25 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2266,7 +2266,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2313,22 +2313,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2390,22 +2390,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2467,28 +2467,28 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2497,7 +2497,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2544,28 +2544,28 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2574,10 +2574,10 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2621,22 +2621,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2651,7 +2651,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2698,28 +2698,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2728,7 +2728,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -2766,7 +2766,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2778,22 +2778,22 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2802,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2816,10 +2816,10 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -2834,16 +2834,16 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -2852,34 +2852,34 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2893,16 +2893,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2911,16 +2911,16 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2929,34 +2929,34 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3006,28 +3006,28 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3065,13 +3065,13 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3080,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3124,28 +3124,28 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3157,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3201,22 +3201,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3263,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3278,28 +3278,28 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3355,22 +3355,22 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3385,7 +3385,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3432,22 +3432,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3509,25 +3509,25 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -3539,10 +3539,10 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3571,10 +3571,10 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3583,7 +3583,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3627,25 +3627,25 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3657,10 +3657,10 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3671,7 +3671,7 @@
         <v>5</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -3686,16 +3686,16 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -3704,34 +3704,34 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>5</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>5</v>
@@ -3793,28 +3793,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>56.76</v>
+        <v>69.44</v>
       </c>
       <c r="G2">
-        <v>43.24</v>
+        <v>30.56</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3825,28 +3825,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>69.44</v>
+        <v>72.97</v>
       </c>
       <c r="G3">
-        <v>30.56</v>
+        <v>27.03</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3866,25 +3866,25 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>77.14</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3898,25 +3898,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="G5">
-        <v>11.11</v>
+        <v>19.44</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3930,16 +3930,16 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>81.08</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G6">
-        <v>18.92</v>
+        <v>13.51</v>
       </c>
       <c r="H6">
         <v>8.1</v>
@@ -3962,25 +3962,25 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4015,166 +4015,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920360</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920383</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920386</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920386</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920419</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920419</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920419</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920399</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4210,36 +4050,36 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920419</v>
+        <v>19330051920359</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920386</v>
+        <v>19330051920358</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4247,61 +4087,61 @@
         <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920383</v>
+        <v>19330051920456</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920399</v>
+        <v>19330051920362</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920359</v>
+        <v>19330051920426</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>125</v>
@@ -4312,13 +4152,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
         <v>126</v>
@@ -4329,16 +4169,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920456</v>
+        <v>19330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4346,16 +4186,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920362</v>
+        <v>19330051920368</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4363,16 +4203,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920426</v>
+        <v>19330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4380,16 +4220,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920366</v>
+        <v>19330051920435</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4397,13 +4237,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920365</v>
+        <v>19330051920371</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
@@ -4414,13 +4254,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920368</v>
+        <v>18330051920097</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -4431,16 +4271,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920367</v>
+        <v>19330051920372</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4448,16 +4288,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920435</v>
+        <v>19330051920373</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4465,16 +4305,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920371</v>
+        <v>19330051920375</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4482,16 +4322,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>18330051920097</v>
+        <v>19330051920374</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4499,16 +4339,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920372</v>
+        <v>19330051920376</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4516,13 +4356,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920373</v>
+        <v>19330051920377</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>136</v>
@@ -4533,13 +4373,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920375</v>
+        <v>19330051920378</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>137</v>
@@ -4550,13 +4390,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920374</v>
+        <v>19330051920381</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
         <v>138</v>
@@ -4567,13 +4407,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920376</v>
+        <v>19330051920382</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
         <v>139</v>
@@ -4584,13 +4424,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920377</v>
+        <v>19330051920383</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>140</v>
@@ -4601,13 +4441,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920378</v>
+        <v>19330051920386</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>141</v>
@@ -4618,13 +4458,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920381</v>
+        <v>19330051920419</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>142</v>
@@ -4635,13 +4475,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920382</v>
+        <v>19330051920389</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -4652,13 +4492,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920389</v>
+        <v>18330051920108</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -4669,13 +4509,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>18330051920108</v>
+        <v>19330051920436</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4686,10 +4526,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920436</v>
+        <v>19330051920391</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
         <v>113</v>
@@ -4703,13 +4543,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920391</v>
+        <v>19330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4720,13 +4560,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920393</v>
+        <v>19330051920394</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4737,13 +4577,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920394</v>
+        <v>19330051920434</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -4754,13 +4594,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920434</v>
+        <v>19330051920396</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>150</v>
@@ -4771,13 +4611,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920396</v>
+        <v>19330051920369</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
         <v>151</v>
@@ -4788,13 +4628,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920369</v>
+        <v>18330051920188</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s">
         <v>152</v>
@@ -4805,13 +4645,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>18330051920188</v>
+        <v>19330051920398</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
         <v>153</v>
@@ -4822,13 +4662,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920398</v>
+        <v>19330051920399</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
         <v>154</v>
@@ -4844,7 +4684,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4876,22 +4716,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920436</v>
+        <v>19330051920358</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4899,19 +4739,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920436</v>
+        <v>19330051920358</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
@@ -4922,22 +4762,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4945,22 +4785,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4968,22 +4808,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920369</v>
+        <v>19330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4991,19 +4831,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920369</v>
+        <v>19330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
@@ -5017,19 +4857,19 @@
         <v>18330051920188</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5040,19 +4880,19 @@
         <v>18330051920188</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5060,19 +4900,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920097</v>
+        <v>19330051920367</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -5083,22 +4923,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920377</v>
+        <v>18330051920108</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5106,47 +4946,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920378</v>
+        <v>19330051920369</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>18330051920108</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20211.xlsx
+++ b/grupos/5ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -194,16 +194,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>
@@ -992,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -1010,7 +1010,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -1087,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1146,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1182,7 +1182,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1472,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1567,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1608,7 +1608,7 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -1626,7 +1626,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1644,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1798,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1857,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2165,7 +2165,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2337,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2396,7 +2396,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2414,7 +2414,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2473,7 +2473,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2627,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2704,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2757,13 +2757,13 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2775,13 +2775,13 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -2840,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -2858,7 +2858,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -2917,7 +2917,7 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -2935,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3012,7 +3012,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3112,7 +3112,7 @@
         <v>4</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -3130,7 +3130,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3148,7 +3148,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3207,7 +3207,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3266,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -3284,7 +3284,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -3302,7 +3302,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3361,7 +3361,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -3379,7 +3379,7 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3438,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>9</v>
@@ -3456,7 +3456,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3515,7 +3515,7 @@
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>9</v>
@@ -3533,7 +3533,7 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3559,7 +3559,7 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -3568,7 +3568,7 @@
         <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
         <v>5</v>
@@ -3633,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
         <v>9</v>
@@ -3692,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -3710,7 +3710,7 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>8</v>
@@ -3728,7 +3728,7 @@
         <v>5</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -3793,28 +3793,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>69.44</v>
+        <v>72.97</v>
       </c>
       <c r="G2">
-        <v>30.56</v>
+        <v>27.03</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3825,28 +3825,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>72.97</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>27.03</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3857,28 +3857,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>80.56</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>19.44</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -3898,19 +3898,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>80.56</v>
+        <v>86.11</v>
       </c>
       <c r="G5">
-        <v>19.44</v>
+        <v>13.89</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4684,7 +4684,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4731,7 +4731,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4754,7 +4754,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4777,7 +4777,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4800,7 +4800,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4831,19 +4831,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
@@ -4869,7 +4869,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4892,7 +4892,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4900,22 +4900,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920367</v>
+        <v>19330051920366</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4938,32 +4938,9 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920369</v>
-      </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
